--- a/JetfWeb/JETFTAX/Download/批量上傳退件原因_範例.xlsx
+++ b/JetfWeb/JETFTAX/Download/批量上傳退件原因_範例.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Source\Jetf\JetfWeb\JETFTAX\Download\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA8F1C0-AFF4-4983-80AA-7F6441AA581E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C63C89-850F-47A8-B580-13BCA084F956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{383CEC6D-FC70-4630-A6C8-CB46EF0EC708}"/>
   </bookViews>
@@ -25,11 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>2511208SJ8DUGS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>單號</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -40,6 +36,14 @@
   </si>
   <si>
     <t>退件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>備註</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TEST</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -439,12 +443,14 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
-        <v>2</v>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
       </c>
-      <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -452,10 +458,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
